--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T08:49:22+00:00</t>
+    <t>2026-03-04T09:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T09:38:55+00:00</t>
+    <t>2026-03-04T10:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T10:43:17+00:00</t>
+    <t>2026-03-04T13:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T13:55:47+00:00</t>
+    <t>2026-03-05T13:54:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:54:22+00:00</t>
+    <t>2026-03-05T14:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T14:12:55+00:00</t>
+    <t>2026-03-05T15:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T15:01:37+00:00</t>
+    <t>2026-03-05T15:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T15:27:35+00:00</t>
+    <t>2026-03-05T16:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T16:09:12+00:00</t>
+    <t>2026-03-06T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T08:12:50+00:00</t>
+    <t>2026-03-09T13:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:07:52+00:00</t>
+    <t>2026-03-17T10:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T10:53:05+00:00</t>
+    <t>2026-06-03T14:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:26:22+00:00</t>
+    <t>2026-06-09T13:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:39+00:00</t>
+    <t>2026-06-11T13:38:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T13:38:26+00:00</t>
+    <t>2026-06-12T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:33:45+00:00</t>
+    <t>2026-06-12T07:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T07:50:14+00:00</t>
+    <t>2026-06-12T13:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:52:17+00:00</t>
+    <t>2026-06-15T09:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T09:04:15+00:00</t>
+    <t>2026-06-16T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:03:26+00:00</t>
+    <t>2026-06-16T13:10:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T13:10:49+00:00</t>
+    <t>2026-06-22T08:40:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
+++ b/449-contenu-fhir---ajout-des-objets-presenceabsence-et-repas/ig/StructureDefinition-tddui-goal-attente.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:40:39+00:00</t>
+    <t>2026-06-24T07:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
